--- a/ig/DM-JANVIER-2025/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM-JANVIER-2025/CodeSystem-terminologie-nabm.xlsx
@@ -31,13 +31,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.215.300.2</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-nabm</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>V93</t>
+    <t>V94</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T00:00:00+00:00</t>
+    <t>2025-01-10T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
